--- a/plantilla/QC-F-002.xlsx
+++ b/plantilla/QC-F-002.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="600" firstSheet="7" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="600" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QC-F-002" sheetId="1" state="visible" r:id="rId1"/>
@@ -1817,7 +1817,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
